--- a/results/havehjornet_mmm_results.xlsx
+++ b/results/havehjornet_mmm_results.xlsx
@@ -19478,10 +19478,10 @@
         <v>705250.740600608</v>
       </c>
       <c r="C2" t="n">
-        <v>423150.444374002</v>
+        <v>423150.444360365</v>
       </c>
       <c r="D2" t="n">
-        <v>-39.9999999980663</v>
+        <v>-40</v>
       </c>
       <c r="E2" t="b">
         <v>0</v>
@@ -19495,10 +19495,10 @@
         <v>159031.875600731</v>
       </c>
       <c r="C3" t="n">
-        <v>122758.323632898</v>
+        <v>101292.957230049</v>
       </c>
       <c r="D3" t="n">
-        <v>-22.8089820552086</v>
+        <v>-36.3065065745955</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -19512,10 +19512,10 @@
         <v>139932.305895969</v>
       </c>
       <c r="C4" t="n">
-        <v>171382.616423873</v>
+        <v>192847.982817445</v>
       </c>
       <c r="D4" t="n">
-        <v>22.4753750226092</v>
+        <v>37.8151968429758</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
@@ -19529,10 +19529,10 @@
         <v>50012.8896329615</v>
       </c>
       <c r="C5" t="n">
-        <v>70018.0454823387</v>
+        <v>70018.0454861461</v>
       </c>
       <c r="D5" t="n">
-        <v>39.9999999923871</v>
+        <v>40</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -19546,10 +19546,10 @@
         <v>48406.0212547538</v>
       </c>
       <c r="C6" t="n">
-        <v>67768.429752909</v>
+        <v>67768.4297566554</v>
       </c>
       <c r="D6" t="n">
-        <v>39.9999999922605</v>
+        <v>40</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
@@ -19563,10 +19563,10 @@
         <v>109668.965388608</v>
       </c>
       <c r="C7" t="n">
-        <v>153536.551537089</v>
+        <v>153536.551544051</v>
       </c>
       <c r="D7" t="n">
-        <v>39.9999999936518</v>
+        <v>40</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -19580,10 +19580,10 @@
         <v>92218.7136439615</v>
       </c>
       <c r="C8" t="n">
-        <v>129106.199100574</v>
+        <v>129106.199101546</v>
       </c>
       <c r="D8" t="n">
-        <v>39.9999999989456</v>
+        <v>40</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -19597,10 +19597,10 @@
         <v>228305.774687954</v>
       </c>
       <c r="C9" t="n">
-        <v>319628.084559185</v>
+        <v>319628.084563135</v>
       </c>
       <c r="D9" t="n">
-        <v>39.9999999982696</v>
+        <v>40</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -19614,10 +19614,10 @@
         <v>188696.479615385</v>
       </c>
       <c r="C10" t="n">
-        <v>264175.071458062</v>
+        <v>264175.071461538</v>
       </c>
       <c r="D10" t="n">
-        <v>39.9999999981578</v>
+        <v>40</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -19761,16 +19761,16 @@
         <v>62</v>
       </c>
       <c r="B5" t="n">
-        <v>2957451.76124513</v>
+        <v>2950834.32667745</v>
       </c>
       <c r="C5" t="n">
-        <v>12.985855913405</v>
+        <v>12.9479450127426</v>
       </c>
       <c r="D5" t="n">
-        <v>0.760010850184393</v>
+        <v>0.761083622210101</v>
       </c>
       <c r="E5" t="n">
-        <v>-6.36084661584389</v>
+        <v>-6.34090197028589</v>
       </c>
     </row>
     <row r="6">
